--- a/runs/taixu-ep03-nirvana-return-20260613-1509/太虚至尊_第三章_标准分镜脚本.xlsx
+++ b/runs/taixu-ep03-nirvana-return-20260613-1509/太虚至尊_第三章_标准分镜脚本.xlsx
@@ -410,7 +410,7 @@
       </ns0:c>
       <ns0:c r="G10" t="inlineStr">
         <ns0:is>
-          <ns0:t>旁白音色：“不管你是谁，不管你在哪，我们都会找到你！”</ns0:t>
+          <ns0:t>旁白音色（太虚古族远古怒吼，低沉压迫、带远古混响）：“尔敢夺我太虚古族神树，不管你是谁，不管你在哪，我们都会找到你！会找到你！！！”</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1187,7 +1187,7 @@
       </ns0:c>
       <ns0:c r="G31" t="inlineStr">
         <ns0:is>
-          <ns0:t>江凡：“筑基境方可摘取。”</ns0:t>
+          <ns0:t>江凡：“最底层果实，筑基境方可摘取。”</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1409,7 +1409,7 @@
       </ns0:c>
       <ns0:c r="G37" t="inlineStr">
         <ns0:is>
-          <ns0:t>王映凤：“争儿，今天复测，千万不要紧张。”</ns0:t>
+          <ns0:t>王映凤：“争儿，今天复测，千万不要紧张，塔主说你上次因为紧张，导致检测结果低于正常水平。”</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1446,7 +1446,7 @@
       </ns0:c>
       <ns0:c r="G38" t="inlineStr">
         <ns0:is>
-          <ns0:t>王映凤：“你上次只是紧张，才检测出三品中等。”</ns0:t>
+          <ns0:t>王映凤：“本来你至少是三品上等，因为紧张，只检测出三品中等！”</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1742,7 +1742,7 @@
       </ns0:c>
       <ns0:c r="G46" t="inlineStr">
         <ns0:is>
-          <ns0:t>陆争：“当个凡人过一辈子，有什么不好呢？”</ns0:t>
+          <ns0:t>陆争：“当个凡人过一辈子，有什么不好呢？何必追求自己得不到的东西？”</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>

--- a/runs/taixu-ep03-nirvana-return-20260613-1509/太虚至尊_第三章_标准分镜脚本.xlsx
+++ b/runs/taixu-ep03-nirvana-return-20260613-1509/太虚至尊_第三章_标准分镜脚本.xlsx
@@ -109,7 +109,7 @@
       </ns0:c>
       <ns0:c r="F2" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2" t="inlineStr">
@@ -146,7 +146,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3" t="inlineStr">
@@ -183,7 +183,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4" t="inlineStr">
@@ -220,7 +220,7 @@
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻震。</ns0:t>
+          <ns0:t>手持拍摄（轻微震动）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5" t="inlineStr">
@@ -257,7 +257,7 @@
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6" t="inlineStr">
@@ -294,7 +294,7 @@
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7" t="inlineStr">
@@ -331,7 +331,7 @@
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8" t="inlineStr">
@@ -368,7 +368,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻震后稳定。</ns0:t>
+          <ns0:t>手持拍摄（轻震后稳定）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9" t="inlineStr">
@@ -405,7 +405,7 @@
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻震。</ns0:t>
+          <ns0:t>手持拍摄（轻微震动）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10" t="inlineStr">
@@ -442,7 +442,7 @@
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11" t="inlineStr">
@@ -479,7 +479,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12" t="inlineStr">
@@ -516,7 +516,7 @@
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13" t="inlineStr">
@@ -553,7 +553,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14" t="inlineStr">
@@ -590,7 +590,7 @@
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15" t="inlineStr">
@@ -627,7 +627,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16" t="inlineStr">
@@ -664,7 +664,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17" t="inlineStr">
@@ -701,7 +701,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18" t="inlineStr">
@@ -738,7 +738,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19" t="inlineStr">
@@ -775,7 +775,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20" t="inlineStr">
@@ -812,7 +812,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21" t="inlineStr">
@@ -849,7 +849,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22" t="inlineStr">
@@ -886,7 +886,7 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23" t="inlineStr">
@@ -923,7 +923,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24" t="inlineStr">
@@ -960,7 +960,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25" t="inlineStr">
@@ -997,7 +997,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </ns0:c>
       <ns0:c r="F46" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G46" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </ns0:c>
       <ns0:c r="F50" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>定镜轻推。</ns0:t>
+          <ns0:t>镜头前推（缓慢轻推）。</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56" t="inlineStr">
